--- a/data/trans_bre/P71_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P71_R-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 10,79</t>
+          <t>-1,64; 10,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 8,41</t>
+          <t>-8,35; 8,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,7; 2,21</t>
+          <t>-13,33; 2,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 10,21</t>
+          <t>-0,04; 10,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 135,37</t>
+          <t>-12,7; 125,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,13; 23,81</t>
+          <t>-19,24; 24,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-33,0; 7,12</t>
+          <t>-32,59; 9,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 277,06</t>
+          <t>-4,98; 322,88</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,59; 16,17</t>
+          <t>4,83; 15,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 9,73</t>
+          <t>-4,11; 9,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 7,93</t>
+          <t>-4,63; 7,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 4,74</t>
+          <t>-4,24; 5,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,65; 75,77</t>
+          <t>17,91; 73,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 19,55</t>
+          <t>-7,04; 18,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 21,34</t>
+          <t>-10,94; 20,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,6; 44,44</t>
+          <t>-25,9; 58,91</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 16,79</t>
+          <t>2,82; 15,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 4,22</t>
+          <t>-7,1; 3,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 15,65</t>
+          <t>1,65; 14,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 10,28</t>
+          <t>-0,9; 9,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,05; 123,82</t>
+          <t>14,71; 120,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-38,15; 31,57</t>
+          <t>-38,34; 32,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,56; 76,23</t>
+          <t>5,87; 68,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 89,01</t>
+          <t>-7,41; 80,36</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,14; 16,64</t>
+          <t>5,57; 16,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 6,7</t>
+          <t>-5,84; 7,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 15,46</t>
+          <t>0,76; 15,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,59; 48,43</t>
+          <t>7,42; 51,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,49; 170,53</t>
+          <t>37,93; 170,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-22,06; 30,34</t>
+          <t>-20,47; 33,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,34; 55,9</t>
+          <t>2,28; 57,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>67,4; 690,28</t>
+          <t>59,56; 619,96</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 14,57</t>
+          <t>-0,92; 13,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 11,09</t>
+          <t>-7,07; 12,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 13,55</t>
+          <t>-4,71; 13,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 3,58</t>
+          <t>-4,72; 3,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 126,49</t>
+          <t>-5,05; 125,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-22,04; 38,08</t>
+          <t>-18,11; 44,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 23,94</t>
+          <t>-7,02; 23,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-56,41; 110,48</t>
+          <t>-59,21; 120,29</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,21; 18,62</t>
+          <t>4,92; 19,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 4,55</t>
+          <t>-7,32; 4,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 6,62</t>
+          <t>-6,7; 7,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 8,07</t>
+          <t>-1,99; 8,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15,49; 105,39</t>
+          <t>18,14; 110,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-40,61; 33,97</t>
+          <t>-36,71; 36,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-30,35; 44,79</t>
+          <t>-31,32; 49,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-11,98; 88,34</t>
+          <t>-13,38; 92,1</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,91; 19,34</t>
+          <t>9,31; 19,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 6,76</t>
+          <t>-2,72; 7,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 7,93</t>
+          <t>-2,67; 7,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 3,33</t>
+          <t>-9,14; 3,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>38,81; 108,59</t>
+          <t>40,79; 112,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 36,09</t>
+          <t>-11,45; 37,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 27,95</t>
+          <t>-8,0; 28,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-57,42; 28,8</t>
+          <t>-61,21; 28,35</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,29; 11,08</t>
+          <t>2,24; 10,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 6,24</t>
+          <t>-3,64; 6,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 5,27</t>
+          <t>-5,6; 4,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,64; 17,14</t>
+          <t>1,06; 17,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,68; 66,78</t>
+          <t>10,11; 65,07</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 20,11</t>
+          <t>-10,3; 21,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 17,67</t>
+          <t>-15,41; 13,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,63; 279,04</t>
+          <t>4,69; 237,36</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,84; 11,97</t>
+          <t>7,68; 11,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 3,6</t>
+          <t>-1,25; 3,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,09; 4,75</t>
+          <t>-0,07; 4,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,41; 9,94</t>
+          <t>1,31; 10,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>40,78; 69,44</t>
+          <t>40,33; 69,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 12,28</t>
+          <t>-3,99; 11,11</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,3; 14,86</t>
+          <t>-0,16; 14,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,46; 83,51</t>
+          <t>10,03; 95,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P71_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P71_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,22</t>
+          <t>2,09</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>27,95%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 10,32</t>
+          <t>-1,8; 10,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 8,93</t>
+          <t>-8,14; 9,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 2,91</t>
+          <t>-13,6; 2,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 10,28</t>
+          <t>-1,75; 6,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 125,0</t>
+          <t>-15,68; 134,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,24; 24,8</t>
+          <t>-18,54; 25,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-32,59; 9,52</t>
+          <t>-32,52; 6,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 322,88</t>
+          <t>-20,21; 117,97</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>1,13</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,83; 15,98</t>
+          <t>5,26; 16,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 9,06</t>
+          <t>-3,93; 9,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 7,73</t>
+          <t>-4,47; 8,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 5,46</t>
+          <t>-3,6; 6,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,91; 73,73</t>
+          <t>18,46; 78,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 18,24</t>
+          <t>-7,07; 17,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 20,52</t>
+          <t>-10,06; 21,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-25,9; 58,91</t>
+          <t>-22,93; 60,05</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,52</t>
+          <t>4,14</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 15,76</t>
+          <t>2,33; 15,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 3,96</t>
+          <t>-6,96; 4,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 14,84</t>
+          <t>1,69; 15,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 9,98</t>
+          <t>-1,29; 9,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,71; 120,69</t>
+          <t>10,65; 117,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-38,34; 32,14</t>
+          <t>-37,49; 37,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,87; 68,67</t>
+          <t>6,15; 70,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 80,36</t>
+          <t>-7,66; 75,31</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22,16</t>
+          <t>6,74</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>207,76%</t>
+          <t>49,08%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,57; 16,37</t>
+          <t>5,86; 16,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 7,47</t>
+          <t>-6,34; 6,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 15,59</t>
+          <t>1,02; 15,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,42; 51,06</t>
+          <t>0,56; 12,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,93; 170,24</t>
+          <t>40,98; 180,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,47; 33,67</t>
+          <t>-22,14; 28,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 57,92</t>
+          <t>3,37; 57,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>59,56; 619,96</t>
+          <t>2,58; 130,16</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,04</t>
+          <t>-0,21</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-0,7%</t>
+          <t>-2,87%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 13,82</t>
+          <t>-1,41; 14,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 12,32</t>
+          <t>-6,94; 12,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 13,17</t>
+          <t>-3,75; 14,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 3,95</t>
+          <t>-4,54; 4,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 125,46</t>
+          <t>-8,72; 128,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,11; 44,17</t>
+          <t>-18,06; 43,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 23,61</t>
+          <t>-5,61; 25,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-59,21; 120,29</t>
+          <t>-46,22; 81,83</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,31</t>
+          <t>2,5</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,92; 19,23</t>
+          <t>3,77; 18,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 4,99</t>
+          <t>-7,51; 5,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 7,02</t>
+          <t>-7,18; 6,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 8,56</t>
+          <t>-2,92; 7,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,14; 110,81</t>
+          <t>15,27; 113,7</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-36,71; 36,82</t>
+          <t>-38,67; 46,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-31,32; 49,04</t>
+          <t>-33,02; 40,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-13,38; 92,1</t>
+          <t>-18,84; 71,56</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,67</t>
+          <t>2,57</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-13,53%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,31; 19,65</t>
+          <t>8,89; 19,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 7,17</t>
+          <t>-2,44; 6,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 7,84</t>
+          <t>-2,45; 8,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 3,21</t>
+          <t>-1,35; 6,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>40,79; 112,18</t>
+          <t>38,35; 107,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,45; 37,68</t>
+          <t>-10,44; 36,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 28,83</t>
+          <t>-7,57; 30,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-61,21; 28,35</t>
+          <t>-9,54; 58,96</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,58</t>
+          <t>1,63</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,24; 10,71</t>
+          <t>2,93; 11,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 6,45</t>
+          <t>-3,55; 6,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 4,15</t>
+          <t>-4,97; 4,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,06; 17,2</t>
+          <t>-2,22; 5,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,11; 65,07</t>
+          <t>13,8; 69,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 21,82</t>
+          <t>-10,02; 20,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-15,41; 13,41</t>
+          <t>-13,91; 15,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,69; 237,36</t>
+          <t>-9,27; 30,68</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4,54</t>
+          <t>2,54</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,68; 11,9</t>
+          <t>7,74; 11,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,31</t>
+          <t>-1,36; 3,37</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 4,59</t>
+          <t>-0,0; 4,54</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,31; 10,0</t>
+          <t>0,99; 4,3</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>40,33; 69,85</t>
+          <t>41,09; 70,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 11,11</t>
+          <t>-4,36; 11,49</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 14,36</t>
+          <t>-0,12; 13,87</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10,03; 95,2</t>
+          <t>6,37; 32,48</t>
         </is>
       </c>
     </row>
